--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,32 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944337</v>
+        <v>128944333</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335463</v>
+        <v>335545</v>
       </c>
       <c r="R7" t="n">
-        <v>6619344</v>
+        <v>6619426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R8" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944360</v>
+        <v>128944337</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335543</v>
+        <v>335463</v>
       </c>
       <c r="R9" t="n">
-        <v>6619392</v>
+        <v>6619344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944333</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>128944337</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -1196,32 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944333</v>
+        <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335545</v>
+        <v>335463</v>
       </c>
       <c r="R7" t="n">
-        <v>6619426</v>
+        <v>6619344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B8" t="n">
         <v>98659</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R8" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944337</v>
+        <v>128944360</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335463</v>
+        <v>335543</v>
       </c>
       <c r="R9" t="n">
-        <v>6619344</v>
+        <v>6619392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944348</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128944370</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R8" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R9" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v>128944338</v>
       </c>
       <c r="B10" t="n">
-        <v>75155</v>
+        <v>75157</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>128944333</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128944348</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128944370</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>128944333</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>128944338</v>
       </c>
       <c r="B10" t="n">
-        <v>75157</v>
+        <v>75159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B8" t="n">
         <v>98678</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R8" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B9" t="n">
         <v>98678</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R9" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -1196,32 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944337</v>
+        <v>128944333</v>
       </c>
       <c r="B7" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335463</v>
+        <v>335545</v>
       </c>
       <c r="R7" t="n">
-        <v>6619344</v>
+        <v>6619426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B8" t="n">
         <v>98678</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R8" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944360</v>
+        <v>128944337</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335543</v>
+        <v>335463</v>
       </c>
       <c r="R9" t="n">
-        <v>6619392</v>
+        <v>6619344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,32 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944333</v>
+        <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335545</v>
+        <v>335463</v>
       </c>
       <c r="R7" t="n">
-        <v>6619426</v>
+        <v>6619344</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
         <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944337</v>
+        <v>128944333</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335463</v>
+        <v>335545</v>
       </c>
       <c r="R9" t="n">
-        <v>6619344</v>
+        <v>6619426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R8" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R9" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128944333</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>128944360</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R8" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R9" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v>128944338</v>
       </c>
       <c r="B10" t="n">
-        <v>75159</v>
+        <v>75161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R8" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944333</v>
+        <v>128944360</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335545</v>
+        <v>335543</v>
       </c>
       <c r="R9" t="n">
-        <v>6619426</v>
+        <v>6619392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
         <v>128944337</v>
       </c>
       <c r="B7" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>128944333</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>128944360</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128944371</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128944364</v>
       </c>
       <c r="B5" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>128944349</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,32 +1196,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944337</v>
+        <v>128944360</v>
       </c>
       <c r="B7" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335463</v>
+        <v>335543</v>
       </c>
       <c r="R7" t="n">
-        <v>6619344</v>
+        <v>6619392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
         <v>128944333</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944360</v>
+        <v>128944337</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>91550</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335543</v>
+        <v>335463</v>
       </c>
       <c r="R9" t="n">
-        <v>6619392</v>
+        <v>6619344</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128944348</v>
+        <v>128944337</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335347</v>
+        <v>335463</v>
       </c>
       <c r="R2" t="n">
-        <v>6619225</v>
+        <v>6619344</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128944370</v>
+        <v>128944371</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,42 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335488</v>
+        <v>335578</v>
       </c>
       <c r="R3" t="n">
-        <v>6619360</v>
+        <v>6619424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128944371</v>
+        <v>128944338</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335578</v>
+        <v>335521</v>
       </c>
       <c r="R4" t="n">
-        <v>6619424</v>
+        <v>6619388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128944364</v>
+        <v>128944348</v>
       </c>
       <c r="B5" t="n">
-        <v>97595</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,34 +989,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335572</v>
+        <v>335347</v>
       </c>
       <c r="R5" t="n">
-        <v>6619436</v>
+        <v>6619225</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,45 +1087,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128944349</v>
+        <v>128944370</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormyråsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335521</v>
+        <v>335488</v>
       </c>
       <c r="R6" t="n">
-        <v>6619367</v>
+        <v>6619360</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128944360</v>
+        <v>128944333</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335543</v>
+        <v>335545</v>
       </c>
       <c r="R7" t="n">
-        <v>6619392</v>
+        <v>6619426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128944333</v>
+        <v>128944339</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335545</v>
+        <v>335554</v>
       </c>
       <c r="R8" t="n">
-        <v>6619426</v>
+        <v>6619468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128944337</v>
+        <v>128944349</v>
       </c>
       <c r="B9" t="n">
-        <v>91550</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335463</v>
+        <v>335521</v>
       </c>
       <c r="R9" t="n">
-        <v>6619344</v>
+        <v>6619367</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,32 +1499,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128944338</v>
+        <v>128944360</v>
       </c>
       <c r="B10" t="n">
-        <v>75161</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335521</v>
+        <v>335543</v>
       </c>
       <c r="R10" t="n">
-        <v>6619388</v>
+        <v>6619392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,6 +1593,107 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128944364</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stormyråsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>335572</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619436</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järnskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 1501-2024 artfynd.xlsx
+++ b/artfynd/A 1501-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944371</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944338</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944348</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944333</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944339</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944349</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944360</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,8 +1748,25 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128944364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>